--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H840"/>
+  <dimension ref="A1:H844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25620,7 +25620,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>362.14</v>
+        <v>368.69</v>
       </c>
       <c r="C840" t="n">
         <v>387.77</v>
@@ -25638,6 +25638,126 @@
         <v>374.21</v>
       </c>
       <c r="H840" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:59:46+00:00</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="C841" t="n">
+        <v>387.77</v>
+      </c>
+      <c r="D841" t="n">
+        <v>391.53</v>
+      </c>
+      <c r="E841" t="n">
+        <v>391.21</v>
+      </c>
+      <c r="F841" t="n">
+        <v>387.54</v>
+      </c>
+      <c r="G841" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="C842" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="D842" t="n">
+        <v>390.83</v>
+      </c>
+      <c r="E842" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="F842" t="n">
+        <v>387.49</v>
+      </c>
+      <c r="G842" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>364.93</v>
+      </c>
+      <c r="C843" t="n">
+        <v>387.28</v>
+      </c>
+      <c r="D843" t="n">
+        <v>390.54</v>
+      </c>
+      <c r="E843" t="n">
+        <v>390.47</v>
+      </c>
+      <c r="F843" t="n">
+        <v>387.47</v>
+      </c>
+      <c r="G843" t="n">
+        <v>375.39</v>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:59:57+00:00</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>363.04</v>
+      </c>
+      <c r="C844" t="n">
+        <v>387</v>
+      </c>
+      <c r="D844" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="E844" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="F844" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="G844" t="n">
+        <v>375.35</v>
+      </c>
+      <c r="H844" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25654,7 +25774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B851"/>
+  <dimension ref="A1:B855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34167,6 +34287,46 @@
       </c>
       <c r="B851" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -34335,28 +34495,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3048443458014085</v>
+        <v>-0.3129539578527233</v>
       </c>
       <c r="J2" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="K2" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1333458380574168</v>
+        <v>0.139679137095583</v>
       </c>
       <c r="M2" t="n">
-        <v>4.51911380819242</v>
+        <v>4.539984258049325</v>
       </c>
       <c r="N2" t="n">
-        <v>34.20537111511241</v>
+        <v>34.38053673879091</v>
       </c>
       <c r="O2" t="n">
-        <v>5.848535809509284</v>
+        <v>5.863491855438268</v>
       </c>
       <c r="P2" t="n">
-        <v>384.0144242185887</v>
+        <v>384.0994149124503</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34413,28 +34573,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2612312826309116</v>
+        <v>-0.264324255889388</v>
       </c>
       <c r="J3" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="K3" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1639843879929379</v>
+        <v>0.1684361606994756</v>
       </c>
       <c r="M3" t="n">
-        <v>3.470328723894063</v>
+        <v>3.468123023909156</v>
       </c>
       <c r="N3" t="n">
-        <v>19.70307027720566</v>
+        <v>19.65880627891379</v>
       </c>
       <c r="O3" t="n">
-        <v>4.438814062022159</v>
+        <v>4.433825242261335</v>
       </c>
       <c r="P3" t="n">
-        <v>397.609670662504</v>
+        <v>397.6420654332618</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34491,28 +34651,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1801236583166625</v>
+        <v>-0.1808838350132133</v>
       </c>
       <c r="J4" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="K4" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1361296218661542</v>
+        <v>0.1384001077315485</v>
       </c>
       <c r="M4" t="n">
-        <v>2.828705667364862</v>
+        <v>2.819379945549774</v>
       </c>
       <c r="N4" t="n">
-        <v>11.66028373926422</v>
+        <v>11.60891326888501</v>
       </c>
       <c r="O4" t="n">
-        <v>3.414715762587601</v>
+        <v>3.40718553484911</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4445541820428</v>
+        <v>396.4525184489884</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34569,28 +34729,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05815002526336027</v>
+        <v>-0.05754642253744691</v>
       </c>
       <c r="J5" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="K5" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01996984133119695</v>
+        <v>0.01977372186891646</v>
       </c>
       <c r="M5" t="n">
-        <v>2.48109346973505</v>
+        <v>2.472277777013751</v>
       </c>
       <c r="N5" t="n">
-        <v>9.398018558238283</v>
+        <v>9.356155359638505</v>
       </c>
       <c r="O5" t="n">
-        <v>3.065618788799136</v>
+        <v>3.058783313613193</v>
       </c>
       <c r="P5" t="n">
-        <v>391.5549602900738</v>
+        <v>391.5486413813683</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34647,28 +34807,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03419707205526894</v>
+        <v>-0.03659878280144728</v>
       </c>
       <c r="J6" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="K6" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003433961679050856</v>
+        <v>0.003968859607801689</v>
       </c>
       <c r="M6" t="n">
-        <v>3.622213737993454</v>
+        <v>3.616149705191895</v>
       </c>
       <c r="N6" t="n">
-        <v>19.22029910886431</v>
+        <v>19.1585796220618</v>
       </c>
       <c r="O6" t="n">
-        <v>4.384096156434564</v>
+        <v>4.377051475829568</v>
       </c>
       <c r="P6" t="n">
-        <v>390.9378134392362</v>
+        <v>390.9629668778371</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34725,28 +34885,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04007163008424887</v>
+        <v>-0.03961166806109338</v>
       </c>
       <c r="J7" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="K7" t="n">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004217869776222072</v>
+        <v>0.004167350155262706</v>
       </c>
       <c r="M7" t="n">
-        <v>3.760123191050841</v>
+        <v>3.745266213041202</v>
       </c>
       <c r="N7" t="n">
-        <v>21.46924820869836</v>
+        <v>21.36955482108231</v>
       </c>
       <c r="O7" t="n">
-        <v>4.633492010211992</v>
+        <v>4.622721581609941</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5355027634163</v>
+        <v>375.5306828141596</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34784,7 +34944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H840"/>
+  <dimension ref="A1:H844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70033,7 +70193,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>-39.300199541841195,176.97752243971212</t>
+          <t>-39.30024469258931,176.97757119304757</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -70062,6 +70222,174 @@
         </is>
       </c>
       <c r="H840" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:59:46+00:00</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>-39.30024469258931,176.97757119304757</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>-39.300785111288896,176.97703562770582</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>-39.30130157459062,176.97651486208684</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>-39.30183905297243,176.97597173528325</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>-39.30235274802415,176.97542625083005</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>-39.30290378338965,176.97491474311542</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>-39.30022725268486,176.977552361599</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>-39.30078220935031,176.97703182915703</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>-39.301297739661514,176.97650843124023</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>-39.301836767744305,176.9759675741856</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>-39.302352528939224,176.97542574506875</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>-39.3029059216185,176.9749209973186</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:53:40+00:00</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>-39.30021877399485,176.97754320639226</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>-39.30078202009346,176.97703158142556</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>-39.30129615090506,176.97650576703253</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>-39.3018352096341,176.97596473707375</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>-39.302352441305274,176.97542554276419</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>-39.302908059847006,176.97492725152213</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:59:57+00:00</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>-39.30020574576219,176.97752913863994</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>-39.300780253695976,176.97702926926559</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>-39.30129483607207,176.9765035621711</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>-39.301832976342716,176.97596067054695</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>-39.302352660390184,176.97542604852552</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>-39.30290791488237,176.97492682750834</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H844"/>
+  <dimension ref="A1:H848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25758,6 +25758,126 @@
         <v>375.35</v>
       </c>
       <c r="H844" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>360.94</v>
+      </c>
+      <c r="C845" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="D845" t="n">
+        <v>389.98</v>
+      </c>
+      <c r="E845" t="n">
+        <v>389.82</v>
+      </c>
+      <c r="F845" t="n">
+        <v>387.69</v>
+      </c>
+      <c r="G845" t="n">
+        <v>375.36</v>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:51+00:00</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>360.41</v>
+      </c>
+      <c r="C846" t="n">
+        <v>386.23</v>
+      </c>
+      <c r="D846" t="n">
+        <v>389.64</v>
+      </c>
+      <c r="E846" t="n">
+        <v>389.31</v>
+      </c>
+      <c r="F846" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="G846" t="n">
+        <v>375.11</v>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>360.01</v>
+      </c>
+      <c r="C847" t="n">
+        <v>386.07</v>
+      </c>
+      <c r="D847" t="n">
+        <v>389.44</v>
+      </c>
+      <c r="E847" t="n">
+        <v>389.09</v>
+      </c>
+      <c r="F847" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="G847" t="n">
+        <v>375.17</v>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>360.19</v>
+      </c>
+      <c r="C848" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="D848" t="n">
+        <v>389.29</v>
+      </c>
+      <c r="E848" t="n">
+        <v>388.85</v>
+      </c>
+      <c r="F848" t="n">
+        <v>387.74</v>
+      </c>
+      <c r="G848" t="n">
+        <v>375.11</v>
+      </c>
+      <c r="H848" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25774,7 +25894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B855"/>
+  <dimension ref="A1:B859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34327,6 +34447,46 @@
       </c>
       <c r="B855" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B857" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B858" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B859" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -34495,28 +34655,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3129539578527233</v>
+        <v>-0.3273865034195768</v>
       </c>
       <c r="J2" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="K2" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="L2" t="n">
-        <v>0.139679137095583</v>
+        <v>0.1482914057234987</v>
       </c>
       <c r="M2" t="n">
-        <v>4.539984258049325</v>
+        <v>4.595058916866295</v>
       </c>
       <c r="N2" t="n">
-        <v>34.38053673879091</v>
+        <v>35.30362080300078</v>
       </c>
       <c r="O2" t="n">
-        <v>5.863491855438268</v>
+        <v>5.94168501378193</v>
       </c>
       <c r="P2" t="n">
-        <v>384.0994149124503</v>
+        <v>384.2508465897725</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34573,28 +34733,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.264324255889388</v>
+        <v>-0.2682416045718017</v>
       </c>
       <c r="J3" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="K3" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1684361606994756</v>
+        <v>0.1735794718625939</v>
       </c>
       <c r="M3" t="n">
-        <v>3.468123023909156</v>
+        <v>3.47005673356994</v>
       </c>
       <c r="N3" t="n">
-        <v>19.65880627891379</v>
+        <v>19.64615967562889</v>
       </c>
       <c r="O3" t="n">
-        <v>4.433825242261335</v>
+        <v>4.432398862425278</v>
       </c>
       <c r="P3" t="n">
-        <v>397.6420654332618</v>
+        <v>397.6831677616742</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34651,28 +34811,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1808838350132133</v>
+        <v>-0.1827615586612334</v>
       </c>
       <c r="J4" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="K4" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1384001077315485</v>
+        <v>0.1420153129062681</v>
       </c>
       <c r="M4" t="n">
-        <v>2.819379945549774</v>
+        <v>2.816105869496892</v>
       </c>
       <c r="N4" t="n">
-        <v>11.60891326888501</v>
+        <v>11.57275415588532</v>
       </c>
       <c r="O4" t="n">
-        <v>3.40718553484911</v>
+        <v>3.401875094104032</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4525184489884</v>
+        <v>396.4722214824382</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34729,28 +34889,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05754642253744691</v>
+        <v>-0.05823340064289436</v>
       </c>
       <c r="J5" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="K5" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01977372186891646</v>
+        <v>0.02045073982026557</v>
       </c>
       <c r="M5" t="n">
-        <v>2.472277777013751</v>
+        <v>2.464029521360238</v>
       </c>
       <c r="N5" t="n">
-        <v>9.356155359638505</v>
+        <v>9.315029207693859</v>
       </c>
       <c r="O5" t="n">
-        <v>3.058783313613193</v>
+        <v>3.052053277335417</v>
       </c>
       <c r="P5" t="n">
-        <v>391.5486413813683</v>
+        <v>391.5558514124911</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34807,28 +34967,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03659878280144728</v>
+        <v>-0.03874077521568288</v>
       </c>
       <c r="J6" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="K6" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003968859607801689</v>
+        <v>0.004488015024802339</v>
       </c>
       <c r="M6" t="n">
-        <v>3.616149705191895</v>
+        <v>3.608965664478865</v>
       </c>
       <c r="N6" t="n">
-        <v>19.1585796220618</v>
+        <v>19.0920016611524</v>
       </c>
       <c r="O6" t="n">
-        <v>4.377051475829568</v>
+        <v>4.369439513387547</v>
       </c>
       <c r="P6" t="n">
-        <v>390.9629668778371</v>
+        <v>390.9854411294685</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34885,28 +35045,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03961166806109338</v>
+        <v>-0.03892419857404363</v>
       </c>
       <c r="J7" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="K7" t="n">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004167350155262706</v>
+        <v>0.004068184936797392</v>
       </c>
       <c r="M7" t="n">
-        <v>3.745266213041202</v>
+        <v>3.731131262314635</v>
       </c>
       <c r="N7" t="n">
-        <v>21.36955482108231</v>
+        <v>21.2711483631335</v>
       </c>
       <c r="O7" t="n">
-        <v>4.622721581609941</v>
+        <v>4.61206552025592</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5306828141596</v>
+        <v>375.5234702204101</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34944,7 +35104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H844"/>
+  <dimension ref="A1:H848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70395,6 +70555,174 @@
         </is>
       </c>
     </row>
+    <row r="845">
+      <c r="A845" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:53:36+00:00</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>-39.300191269945806,176.97751350781022</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>-39.3007783611272,176.9770267919515</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>-39.301293082961365,176.97650062235596</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>-39.30183183372845,176.97595858999844</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>-39.30235340527888,176.97542776811406</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>-39.30290795112352,176.97492693351177</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:51+00:00</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>-39.3001876165251,176.97750956288755</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>-39.30077539610266,176.97702291082626</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>-39.30129122028114,176.97649749880256</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>-39.30182918494067,176.975953766909</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>-39.30235344909587,176.97542786926633</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>-39.30290704509454,176.9749242834255</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>-39.30018485922634,176.97750658558772</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>-39.30077438673256,176.97702158959225</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>-39.301290124586835,176.97649566141826</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>-39.301828042326285,176.9759516863607</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>-39.30235344909587,176.97542786926633</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>-39.302907262541495,176.9749249194462</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>-39.300186100010784,176.9775079253726</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>-39.300776910157765,176.9770248926774</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>-39.3012893028161,176.97649428338008</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>-39.30182679583779,176.97594941667177</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>-39.30235362436378,176.9754282738754</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>-39.30290704509454,176.9749242834255</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0290/nzd0290.xlsx
+++ b/data/nzd0290/nzd0290.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H848"/>
+  <dimension ref="A1:H851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25880,6 +25880,96 @@
       <c r="H848" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>360.51</v>
+      </c>
+      <c r="C849" t="n">
+        <v>386.66</v>
+      </c>
+      <c r="D849" t="n">
+        <v>389.32</v>
+      </c>
+      <c r="E849" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="F849" t="n">
+        <v>387.95</v>
+      </c>
+      <c r="G849" t="n">
+        <v>374.66</v>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>360.71</v>
+      </c>
+      <c r="C850" t="n">
+        <v>386.57</v>
+      </c>
+      <c r="D850" t="n">
+        <v>389.24</v>
+      </c>
+      <c r="E850" t="n">
+        <v>388.33</v>
+      </c>
+      <c r="F850" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="G850" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>359.44</v>
+      </c>
+      <c r="C851" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="D851" t="n">
+        <v>388.64</v>
+      </c>
+      <c r="E851" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="F851" t="n">
+        <v>388.42</v>
+      </c>
+      <c r="G851" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25894,7 +25984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B859"/>
+  <dimension ref="A1:B862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34487,6 +34577,36 @@
       </c>
       <c r="B859" t="n">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B860" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B861" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B862" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -34655,28 +34775,28 @@
         <v>0.0479</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3273865034195768</v>
+        <v>-0.3381001825327613</v>
       </c>
       <c r="J2" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="K2" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1482914057234987</v>
+        <v>0.1547185194862152</v>
       </c>
       <c r="M2" t="n">
-        <v>4.595058916866295</v>
+        <v>4.636984568428827</v>
       </c>
       <c r="N2" t="n">
-        <v>35.30362080300078</v>
+        <v>35.98310288387059</v>
       </c>
       <c r="O2" t="n">
-        <v>5.94168501378193</v>
+        <v>5.998591741723268</v>
       </c>
       <c r="P2" t="n">
-        <v>384.2508465897725</v>
+        <v>384.363698641166</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34733,28 +34853,28 @@
         <v>0.0776</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2682416045718017</v>
+        <v>-0.2709219220139075</v>
       </c>
       <c r="J3" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="K3" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1735794718625939</v>
+        <v>0.177271057144517</v>
       </c>
       <c r="M3" t="n">
-        <v>3.47005673356994</v>
+        <v>3.470554311618616</v>
       </c>
       <c r="N3" t="n">
-        <v>19.64615967562889</v>
+        <v>19.62709317031029</v>
       </c>
       <c r="O3" t="n">
-        <v>4.432398862425278</v>
+        <v>4.430247529236971</v>
       </c>
       <c r="P3" t="n">
-        <v>397.6831677616742</v>
+        <v>397.7113996912362</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34811,28 +34931,28 @@
         <v>0.0718</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1827615586612334</v>
+        <v>-0.1844990267784443</v>
       </c>
       <c r="J4" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="K4" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1420153129062681</v>
+        <v>0.1451221234461375</v>
       </c>
       <c r="M4" t="n">
-        <v>2.816105869496892</v>
+        <v>2.815432668545975</v>
       </c>
       <c r="N4" t="n">
-        <v>11.57275415588532</v>
+        <v>11.55333483151585</v>
       </c>
       <c r="O4" t="n">
-        <v>3.401875094104032</v>
+        <v>3.399019686838523</v>
       </c>
       <c r="P4" t="n">
-        <v>396.4722214824382</v>
+        <v>396.4905247440603</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34889,28 +35009,28 @@
         <v>0.0693</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05823340064289436</v>
+        <v>-0.05938888661886315</v>
       </c>
       <c r="J5" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="K5" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02045073982026557</v>
+        <v>0.02140282043811648</v>
       </c>
       <c r="M5" t="n">
-        <v>2.464029521360238</v>
+        <v>2.461036224234596</v>
       </c>
       <c r="N5" t="n">
-        <v>9.315029207693859</v>
+        <v>9.29163338785699</v>
       </c>
       <c r="O5" t="n">
-        <v>3.052053277335417</v>
+        <v>3.048218067635088</v>
       </c>
       <c r="P5" t="n">
-        <v>391.5558514124911</v>
+        <v>391.5680238031948</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34967,28 +35087,28 @@
         <v>0.0736</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03874077521568288</v>
+        <v>-0.04000565257769011</v>
       </c>
       <c r="J6" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="K6" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004488015024802339</v>
+        <v>0.004820786334993277</v>
       </c>
       <c r="M6" t="n">
-        <v>3.608965664478865</v>
+        <v>3.602079675061218</v>
       </c>
       <c r="N6" t="n">
-        <v>19.0920016611524</v>
+        <v>19.03596415077158</v>
       </c>
       <c r="O6" t="n">
-        <v>4.369439513387547</v>
+        <v>4.363022364230051</v>
       </c>
       <c r="P6" t="n">
-        <v>390.9854411294685</v>
+        <v>390.9987625479757</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35045,28 +35165,28 @@
         <v>0.0537</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03892419857404363</v>
+        <v>-0.03878840461601308</v>
       </c>
       <c r="J7" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="K7" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004068184936797392</v>
+        <v>0.004073067940179143</v>
       </c>
       <c r="M7" t="n">
-        <v>3.731131262314635</v>
+        <v>3.718655914543091</v>
       </c>
       <c r="N7" t="n">
-        <v>21.2711483631335</v>
+        <v>21.19621929389959</v>
       </c>
       <c r="O7" t="n">
-        <v>4.61206552025592</v>
+        <v>4.603935196535632</v>
       </c>
       <c r="P7" t="n">
-        <v>375.5234702204101</v>
+        <v>375.5220394973906</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35104,7 +35224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H848"/>
+  <dimension ref="A1:H851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70723,6 +70843,132 @@
         </is>
       </c>
     </row>
+    <row r="849">
+      <c r="A849" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:53:51+00:00</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>-39.30018830584978,176.97751030721255</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>-39.30077810878469,176.97702646164294</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>-39.30128946717025,176.97649455898772</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>-39.30182549741224,176.9759470524125</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>-39.30235454452036,176.97543039807306</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>-39.3029054142422,176.97491951327038</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>-39.3001896844991,176.9775117958626</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>-39.30077754101405,176.97702571844874</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>-39.30128902889251,176.976493824034</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>-39.30182409511258,176.97594449901263</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>-39.3023550703241,176.97543161190035</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>-39.30290512431288,176.97491866524282</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:08+00:00</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>-39.30018093007544,176.97750234293582</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>-39.30077804569906,176.97702637906582</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>-39.30128574180935,176.97648831188167</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>-39.30182290056097,176.9759423238943</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>-39.30235660391826,176.97543515222995</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>-39.30290574041269,176.9749204673014</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
